--- a/dropBD/coffee.xlsx
+++ b/dropBD/coffee.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinapuskova/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ekaterinapuskova/Drop_Coffe/dropBD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13B0522F-A3F2-434F-B4B5-3834D85B6F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0578D84B-0E04-E147-8BF4-2587E801F0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="520" windowWidth="28800" windowHeight="16340" xr2:uid="{A3841751-509E-FF45-8274-2AD8FE4E2E00}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{A3841751-509E-FF45-8274-2AD8FE4E2E00}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <t>coffe_name</t>
   </si>
@@ -201,6 +201,84 @@
   </si>
   <si>
     <t>Согревающий чай с ярким вкусом малины и карамельными нотками сиропа топинамбура. Ароматный, сладкий, уютный — как объятие в чашке!</t>
+  </si>
+  <si>
+    <t>Americano.png</t>
+  </si>
+  <si>
+    <t>cappuccino.png</t>
+  </si>
+  <si>
+    <t>Americano2.png</t>
+  </si>
+  <si>
+    <t>cappuccino2.png</t>
+  </si>
+  <si>
+    <t>cappuccinoXL.png</t>
+  </si>
+  <si>
+    <t>Latin.png</t>
+  </si>
+  <si>
+    <t>LatinXL.png</t>
+  </si>
+  <si>
+    <t>Pine_Nut_Latte.png</t>
+  </si>
+  <si>
+    <t>Flat_White.png</t>
+  </si>
+  <si>
+    <t>White_Chocolate_Latte.png</t>
+  </si>
+  <si>
+    <t>Citrus_latte.png</t>
+  </si>
+  <si>
+    <t> Pistachio_Latte.png</t>
+  </si>
+  <si>
+    <t>Vanilla_milkshake.png</t>
+  </si>
+  <si>
+    <t>Ice_Latte.png</t>
+  </si>
+  <si>
+    <t>Ice-Americano.png</t>
+  </si>
+  <si>
+    <t>Fresh_Orange.png</t>
+  </si>
+  <si>
+    <t>Bronekofe.png</t>
+  </si>
+  <si>
+    <t>Matcha_Latte.png</t>
+  </si>
+  <si>
+    <t>Small_cocoa.png</t>
+  </si>
+  <si>
+    <t>Big_cocoa.png</t>
+  </si>
+  <si>
+    <t>Hot_chocolate.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Masala_Latte_XL.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Masala_Latte.png</t>
+  </si>
+  <si>
+    <t>Berry_rosehip.png</t>
+  </si>
+  <si>
+    <t>Raspberry_Crash.png</t>
+  </si>
+  <si>
+    <t>Tea_assortment.png</t>
   </si>
 </sst>
 </file>
@@ -616,6 +694,7 @@
     <col min="1" max="1" width="37.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.1640625" customWidth="1"/>
     <col min="3" max="3" width="169.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -645,7 +724,9 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -660,7 +741,9 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -675,7 +758,9 @@
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -690,7 +775,9 @@
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -705,7 +792,9 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -720,7 +809,9 @@
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -735,7 +826,9 @@
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -750,7 +843,9 @@
       <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -765,7 +860,9 @@
       <c r="C10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -780,7 +877,9 @@
       <c r="C11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -795,7 +894,9 @@
       <c r="C12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="E12" s="4"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -810,7 +911,9 @@
       <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -835,7 +938,9 @@
       <c r="C14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -860,7 +965,9 @@
       <c r="C15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -885,7 +992,9 @@
       <c r="C16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -910,7 +1019,9 @@
       <c r="C17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -935,7 +1046,9 @@
       <c r="C18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -960,7 +1073,9 @@
       <c r="C19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -985,7 +1100,9 @@
       <c r="C20" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -1010,7 +1127,9 @@
       <c r="C21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -1035,7 +1154,9 @@
       <c r="C22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -1060,7 +1181,9 @@
       <c r="C23" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -1085,7 +1208,9 @@
       <c r="C24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -1110,7 +1235,9 @@
       <c r="C25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -1135,7 +1262,9 @@
       <c r="C26" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -1160,7 +1289,9 @@
       <c r="C27" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
